--- a/out/27S/ver2/27S_ver2_room.xlsx
+++ b/out/27S/ver2/27S_ver2_room.xlsx
@@ -84,7 +84,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +113,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E6FFFF"/>
       </patternFill>
     </fill>
@@ -123,12 +128,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
+        <fgColor rgb="00F5F5DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E6FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -207,23 +217,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -650,7 +666,7 @@
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>MATH 1914-001
-Jordan, Susan M.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -658,15 +674,21 @@
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>MATH 1914-001
-Jordan, Susan M.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1914-001
+Growns, Landon C.
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>MATH 1914-001
-Jordan, Susan M.
+Growns, Landon C.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -680,7 +702,7 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="7" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -689,7 +711,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>MATH 2914-001
 Jordan, Susan M.
@@ -697,15 +719,15 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>MATH 2914-001
 Jordan, Susan M.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>MATH 2914-001
 Jordan, Susan M.
@@ -720,17 +742,17 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1914-001
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
 Jordan, Susan M.
 9:30 AM-10:50 AM</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2914-001
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>MATH 2703-002
 Jordan, Susan M.
 9:30 AM-10:50 AM</t>
         </is>
@@ -743,26 +765,26 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>MATH 2703-001
-Overduin, Matthew D.
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MATH 2703-001
-Overduin, Matthew D.
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>MATH 2703-001
-Overduin, Matthew D.
+Jordan, Susan M.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -785,13 +807,7 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2934-002
-Staff
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
           <t>MATH 4971-001
@@ -799,27 +815,15 @@
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>MATH 2934-002
-Staff
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2934-002
-Staff
+Limperis, Thomas G.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>MATH 2934-002
-Staff
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -827,11 +831,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -863,7 +867,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>MATH 2914-002
 Jordan, Susan M.
@@ -871,21 +875,21 @@
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>MATH 2914-002
 Jordan, Susan M.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>MATH 2914-002
 Jordan, Susan M.
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>MATH 2914-002
 Jordan, Susan M.
@@ -902,7 +906,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -911,26 +915,26 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Yousuf, Marium
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Jordan, Susan M.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Yousuf, Marium
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Jordan, Susan M.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Yousuf, Marium
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>MATH 1003-007
+Jordan, Susan M.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
@@ -942,9 +946,21 @@
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2914-001
+Jordan, Susan M.
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Limperis, Thomas G.
+2:30 PM-3:50 PM</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -954,9 +970,9 @@
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="C17" s="7" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="5" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -966,9 +982,9 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="6" t="n"/>
       <c r="F18" s="5" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1003,21 +1019,21 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="E16:E18"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C16:C18"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="C9:C11"/>
@@ -1114,29 +1130,11 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>MATH 4003-001
-Xiao, Xinli
-9:00 AM-9:50 AM</t>
-        </is>
-      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1144,17 +1142,17 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>MATH 2924-003
-Limperis, Thomas G.
+Xiao, Xinli
 9:30 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1177,7 +1175,7 @@
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="13" t="inlineStr">
         <is>
           <t>MATH 3243-001
@@ -1204,23 +1202,29 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Limperis, Thomas G.
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2703-002
-Limperis, Thomas G.
-11:00 AM-12:20 PM</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>MATH 4003-001
+Xiao, Xinli
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1228,11 +1232,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1240,29 +1244,11 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Limperis, Thomas G.
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Limperis, Thomas G.
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-002
-Limperis, Thomas G.
-12:00 PM-12:50 PM</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1270,11 +1256,11 @@
           <t>12:30 PM</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="5" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1286,7 +1272,7 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t>MATH 2924-002
-Limperis, Thomas G.
+Yousuf, Marium
 1:00 PM-2:20 PM</t>
         </is>
       </c>
@@ -1301,7 +1287,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="7" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -1312,11 +1298,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Yousuf, Marium
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Yousuf, Marium
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-002
+Yousuf, Marium
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1324,11 +1328,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1380,20 +1384,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="14">
+  <mergeCells count="12">
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D11:D12"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="E6:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1487,7 +1489,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Jordan, Scott M.
@@ -1495,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Jordan, Scott M.
@@ -1503,7 +1505,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>STAT 3153-001
 Jordan, Scott M.
@@ -1521,7 +1523,7 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>MATH 2934-001
-Staff
+Yousuf, Marium
 9:30 AM-10:50 AM</t>
         </is>
       </c>
@@ -1538,15 +1540,15 @@
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>MATH 2934-001
-Staff
+Yousuf, Marium
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="7" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>MATH 2934-001
-Staff
+Yousuf, Marium
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -1554,7 +1556,7 @@
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>MATH 2934-001
-Staff
+Yousuf, Marium
 10:00 AM-10:50 AM</t>
         </is>
       </c>
@@ -1818,11 +1820,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 3243-002
+Limperis, Thomas G.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1830,11 +1850,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1914,29 +1934,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Xiao, Xinli
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Xiao, Xinli
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 3243-002
-Xiao, Xinli
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1944,11 +1946,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -2025,10 +2027,10 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="4">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -2097,11 +2099,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>STAT 3113-001
+Xiao, Xinli
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2109,11 +2129,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2169,29 +2189,11 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>STAT 3113-001
-Xiao, Xinli
-11:00 AM-11:50 AM</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2199,11 +2201,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -2235,7 +2237,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Jordan, Scott M.
@@ -2243,7 +2245,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Jordan, Scott M.
@@ -2251,7 +2253,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>STAT 3183-001
 Jordan, Scott M.
@@ -2347,12 +2349,12 @@
   <autoFilter ref="A2:F20"/>
   <mergeCells count="7">
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="F9:F10"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -2421,29 +2423,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-Winn, Janet L.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-Winn, Janet L.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>MATH 1003-006
-Winn, Janet L.
-8:00 AM-8:50 AM</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2451,11 +2435,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2463,11 +2447,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-006
+King, Jamie L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2475,11 +2477,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2487,7 +2489,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>STAT 2163-001
 King, Jamie L.
@@ -2495,7 +2497,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>STAT 2163-001
 King, Jamie L.
@@ -2503,7 +2505,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>STAT 2163-001
 King, Jamie L.
@@ -2703,15 +2705,15 @@
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -2804,11 +2806,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Xiao, Xinli
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Xiao, Xinli
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2924-003
+Xiao, Xinli
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2816,11 +2836,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2828,29 +2848,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Limperis, Thomas G.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Limperis, Thomas G.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 2924-003
-Limperis, Thomas G.
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -2858,11 +2860,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -3011,10 +3013,10 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="4">
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3084,9 +3086,21 @@
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Taylor, Teresa L.
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>MATH 1113-006
+Taylor, Teresa L.
+8:00 AM-9:20 AM</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -3096,9 +3110,9 @@
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="7" t="n"/>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="7" t="n"/>
       <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3107,23 +3121,23 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>MATH 2043-001
 Taylor, Teresa L.
@@ -3155,7 +3169,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Taylor, Teresa L.
@@ -3163,15 +3177,15 @@
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Taylor, Teresa L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>MATH 2033-001
 Taylor, Teresa L.
@@ -3240,9 +3254,9 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="7" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -3275,7 +3289,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>MATH 2924-001
 Yousuf, Marium
@@ -3283,21 +3297,21 @@
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>MATH 2924-001
 Yousuf, Marium
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>MATH 2924-001
 Yousuf, Marium
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>MATH 2924-001
 Yousuf, Marium
@@ -3314,7 +3328,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3323,7 +3337,7 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -3331,7 +3345,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -3339,7 +3353,7 @@
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>MATH 3123-001
 Overduin, Matthew D.
@@ -3409,12 +3423,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
@@ -3422,9 +3438,9 @@
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E13:E15"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="F7:F8"/>
@@ -3522,26 +3538,26 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-001
-Winn, Janet L.
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Cox, Allie M.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-001
-Winn, Janet L.
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Cox, Allie M.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-001
-Winn, Janet L.
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>MATH 2223-001
+Cox, Allie M.
 9:00 AM-9:50 AM</t>
         </is>
       </c>
@@ -3553,7 +3569,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Winn, Janet L.
@@ -3561,7 +3577,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>MATH 0803-001
 Winn, Janet L.
@@ -3583,7 +3599,7 @@
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="7" t="n"/>
       <c r="D7" s="10" t="inlineStr">
         <is>
           <t>MATH 2223-003
@@ -3591,7 +3607,7 @@
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="10" t="inlineStr">
         <is>
           <t>MATH 2223-003
@@ -3618,38 +3634,38 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Cox, Allie M.
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>MATH 2223-002
 Cox, Allie M.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Cox, Allie M.
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>MATH 2223-002
 Cox, Allie M.
 11:00 AM-12:20 PM</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>MATH 2223-001
-Cox, Allie M.
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>MATH 2934-002
+Limperis, Thomas G.
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -3661,9 +3677,9 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="7" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -3696,7 +3712,7 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Ballard, Kasey L.
@@ -3704,7 +3720,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Ballard, Kasey L.
@@ -3712,7 +3728,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>MATH 0803-003
 Ballard, Kasey L.
@@ -3738,7 +3754,7 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Ballard, Kasey L.
@@ -3746,7 +3762,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Ballard, Kasey L.
@@ -3754,7 +3770,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-003
 Ballard, Kasey L.
@@ -3913,38 +3929,38 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Growns, Landon C.
+Winn, Janet L.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>MATH 1113-002
-Growns, Landon C.
+Winn, Janet L.
 8:00 AM-9:20 AM</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Growns, Landon C.
+Winn, Janet L.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>MATH 1113-002
-Growns, Landon C.
+Winn, Janet L.
 8:00 AM-9:20 AM</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>MATH 0903-002
-Growns, Landon C.
+Winn, Janet L.
 8:00 AM-8:50 AM</t>
         </is>
       </c>
@@ -3956,9 +3972,9 @@
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="7" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="7" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3967,7 +3983,7 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3975,7 +3991,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3983,7 +3999,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>STAT 2163-002
 Bain, Leslie M.
@@ -3998,21 +4014,9 @@
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Taylor, Teresa L.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>MATH 1113-006
-Taylor, Teresa L.
-9:30 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4021,23 +4025,23 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Winn, Janet L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Winn, Janet L.
 10:00 AM-10:50 AM</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>MATH 1003-005
 Winn, Janet L.
@@ -4052,9 +4056,9 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
       <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4066,35 +4070,35 @@
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Staff
 11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>MATH 0903-001
-Yousuf, Marium
+Staff
 11:00 AM-12:20 PM</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Staff
 11:00 AM-11:50 AM</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>MATH 0903-001
-Yousuf, Marium
+Staff
 11:00 AM-12:20 PM</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>MATH 1113-001
-Yousuf, Marium
+Staff
 11:00 AM-11:50 AM</t>
         </is>
       </c>
@@ -4106,9 +4110,9 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="7" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="9" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4141,38 +4145,38 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Cox, Allie M.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>STAT 2163-003
 Bain, Leslie M.
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Cox, Allie M.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>STAT 2163-003
 Bain, Leslie M.
 1:00 PM-2:20 PM</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>MATH 2243-001
-Cox, Allie M.
+Overduin, Matthew D.
 1:00 PM-1:50 PM</t>
         </is>
       </c>
@@ -4184,9 +4188,9 @@
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="7" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -4195,11 +4199,29 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Bain, Leslie M.
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Bain, Leslie M.
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>STAT 2163-004
+Bain, Leslie M.
+2:00 PM-2:50 PM</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -4207,11 +4229,11 @@
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -4263,7 +4285,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F6"/>
@@ -4274,13 +4297,13 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E6:E8"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="A1:F1"/>
@@ -4380,11 +4403,29 @@
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-001
+Winn, Janet L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-001
+Winn, Janet L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1003-001
+Winn, Janet L.
+9:00 AM-9:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -4392,11 +4433,11 @@
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4404,11 +4445,29 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>MATH 1003-004
+Staff 2
+10:00 AM-10:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -4416,11 +4475,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -4428,11 +4487,29 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff 2
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff 2
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>MATH 0803-004
+Staff 2
+11:00 AM-11:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -4440,11 +4517,11 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -4476,29 +4553,11 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Winn, Janet L.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Winn, Janet L.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1003-007
-Winn, Janet L.
-1:00 PM-1:50 PM</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -4506,11 +4565,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -4586,11 +4645,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="4">
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="10">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4659,32 +4724,11 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>MATH 3203-001
-Overduin, Matthew D.
-8:00 AM-8:50 AM
-/ MATH 3203-H01</t>
-        </is>
-      </c>
+      <c r="F3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -4692,11 +4736,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4818,11 +4862,32 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>MATH 4123-001
+Limperis, Thomas G.
+1:00 PM-1:50 PM
+/ MATH 4123-H01</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -4830,11 +4895,11 @@
           <t>1:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -4842,26 +4907,26 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-King, Jamie L.
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Limperis, Thomas G.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-King, Jamie L.
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Limperis, Thomas G.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>STAT 2163-004
-King, Jamie L.
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>MATH 2914-003
+Limperis, Thomas G.
 2:00 PM-2:50 PM</t>
         </is>
       </c>
@@ -4875,13 +4940,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>MATH 2914-003
-Yousuf, Marium
-2:30 PM-3:50 PM</t>
-        </is>
-      </c>
+      <c r="E16" s="5" t="n"/>
       <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -4893,7 +4952,7 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="9" t="n"/>
+      <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -4905,7 +4964,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -4934,16 +4993,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:F20"/>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="B15:B16"/>
   </mergeCells>
@@ -5014,11 +5072,29 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MATH 1113-F01
+Yousuf, Marium
+8:00 AM-8:50 AM</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5026,11 +5102,11 @@
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5062,29 +5138,11 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>MATH 1113-F01
-Yousuf, Marium
-10:00 AM-10:50 AM</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5092,11 +5150,11 @@
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -5245,10 +5303,10 @@
   </sheetData>
   <autoFilter ref="A2:F20"/>
   <mergeCells count="4">
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -5378,9 +5436,9 @@
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="7" t="n"/>
       <c r="D7" s="5" t="n"/>
-      <c r="E7" s="9" t="n"/>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
